--- a/STARTS/START1.xlsx
+++ b/STARTS/START1.xlsx
@@ -491,7 +491,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>

--- a/STARTS/START1.xlsx
+++ b/STARTS/START1.xlsx
@@ -470,15 +470,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="28" customHeight="1"/>
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="28" customHeight="1"/>
   <cols>
-    <col width="65.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="54.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="73.5" customWidth="1" style="2" min="3" max="3"/>
-    <col width="25.6640625" customWidth="1" style="2" min="4" max="4"/>
-    <col width="8.83203125" customWidth="1" style="2" min="5" max="13"/>
-    <col width="8.83203125" customWidth="1" style="2" min="14" max="16384"/>
+    <col width="65.1796875" customWidth="1" style="2" min="1" max="1"/>
+    <col width="54.6328125" customWidth="1" style="2" min="2" max="2"/>
+    <col width="73.453125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="25.6328125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="8.81640625" customWidth="1" style="2" min="5" max="15"/>
+    <col width="8.81640625" customWidth="1" style="2" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -487,119 +487,174 @@
           <t>Title</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>used_project</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>used_project</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>used.1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>used_at.1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>used_project.1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Column_8</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Column_9</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Column_10</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Column_11</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Column_12</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Column_13</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Column_14</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Column_15</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Column_16</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>pizza</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Creamy Garlic Chicken Pasta</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:07:33</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>A2-Pinterest_02</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Spicy Honey Glazed Salmon</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:07:33</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New site (p04)</t>
+        </is>
+      </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="3" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="3" t="n"/>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="3" t="n"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="3" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="3" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="3" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="3" t="n"/>
-    </row>
+    <row r="5" ht="28" customHeight="1"/>
+    <row r="6" ht="28" customHeight="1"/>
+    <row r="7" ht="28" customHeight="1"/>
+    <row r="8" ht="28" customHeight="1"/>
+    <row r="9" ht="28" customHeight="1"/>
+    <row r="10" ht="28" customHeight="1"/>
+    <row r="11" ht="28" customHeight="1"/>
+    <row r="12" ht="28" customHeight="1"/>
+    <row r="13" ht="28" customHeight="1"/>
+    <row r="14" ht="28" customHeight="1"/>
+    <row r="15" ht="28" customHeight="1"/>
+    <row r="16" ht="28" customHeight="1"/>
+    <row r="17" ht="28" customHeight="1"/>
+    <row r="18" ht="28" customHeight="1"/>
+    <row r="19" ht="28" customHeight="1"/>
+    <row r="20" ht="28" customHeight="1"/>
+    <row r="21" ht="28" customHeight="1"/>
+    <row r="22" ht="28" customHeight="1"/>
+    <row r="23" ht="28" customHeight="1"/>
+    <row r="24" ht="28" customHeight="1"/>
+    <row r="25" ht="28" customHeight="1"/>
+    <row r="26" ht="28" customHeight="1"/>
+    <row r="27" ht="28" customHeight="1"/>
+    <row r="28" ht="28" customHeight="1"/>
+    <row r="29" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
